--- a/core/src/main/java/com/avoid/util/GameState_Template.xlsx
+++ b/core/src/main/java/com/avoid/util/GameState_Template.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\info\Documents\20. Nici\LibGdx\avoid-ashley\core\src\main\java\com\avoid\util\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B58204-2226-4BB1-BC84-9F2322F73D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="150" windowWidth="32595" windowHeight="14505"/>
+    <workbookView xWindow="7785" yWindow="675" windowWidth="16470" windowHeight="12750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
   <si>
     <t xml:space="preserve">                         COMPONENT
 ENTITY</t>
@@ -31,11 +37,17 @@
     <t xml:space="preserve">                         COMPONENT
 SYSTEM</t>
   </si>
+  <si>
+    <t>GridRenderSystem</t>
+  </si>
+  <si>
+    <t>zeichnet das Raster der Spielwelt</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -169,7 +181,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="2" applyFont="1" applyBorder="1"/>
@@ -180,17 +192,11 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -203,15 +209,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Neutral" xfId="2" builtinId="28"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Schlecht" xfId="1" builtinId="27"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -219,14 +221,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -264,7 +269,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -336,7 +341,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -509,9 +514,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.28515625" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" customWidth="1"/>
@@ -527,128 +532,133 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="15"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="11"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-    </row>
-    <row r="14" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -658,35 +668,35 @@
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
     </row>
-    <row r="15" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-    </row>
-    <row r="16" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
     </row>
     <row r="19" spans="1:11" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="1:11" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -705,7 +715,9 @@
       <c r="K20" s="4"/>
     </row>
     <row r="21" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
+      <c r="A21" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -759,7 +771,7 @@
     <row r="25" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="1"/>
-      <c r="C25" s="18"/>
+      <c r="C25" s="7"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -847,7 +859,7 @@
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
     </row>
-    <row r="32" spans="1:11" s="8" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -860,44 +872,8 @@
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
     </row>
-    <row r="33" spans="1:11" s="8" customFormat="1" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K35" s="11"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K36" s="11"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K37" s="11"/>
-    </row>
-    <row r="38" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K38" s="11"/>
-    </row>
+    <row r="33" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="39" spans="1:11" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>0</v>
@@ -975,18 +951,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/core/src/main/java/com/avoid/util/GameState_Template.xlsx
+++ b/core/src/main/java/com/avoid/util/GameState_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\info\Documents\20. Nici\LibGdx\avoid-ashley\core\src\main\java\com\avoid\util\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B58204-2226-4BB1-BC84-9F2322F73D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00ADADC-5153-440C-9AD7-FFBE30212BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7785" yWindow="675" windowWidth="16470" windowHeight="12750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
   <si>
     <t xml:space="preserve">                         COMPONENT
 ENTITY</t>
@@ -42,6 +42,12 @@
   </si>
   <si>
     <t>zeichnet das Raster der Spielwelt</t>
+  </si>
+  <si>
+    <t>DebugCameraSystem</t>
+  </si>
+  <si>
+    <t>Steuert die Debug Kamera ( Bewegung und Zoom)</t>
   </si>
 </sst>
 </file>
@@ -559,7 +565,12 @@
       <c r="I3" s="12"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="8"/>
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>7</v>
+      </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -730,7 +741,9 @@
       <c r="K21" s="1"/>
     </row>
     <row r="22" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
+      <c r="A22" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>

--- a/core/src/main/java/com/avoid/util/GameState_Template.xlsx
+++ b/core/src/main/java/com/avoid/util/GameState_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\info\Documents\20. Nici\LibGdx\avoid-ashley\core\src\main\java\com\avoid\util\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\Java\LibGDX\avoid-ashley\core\src\main\java\com\avoid\util\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00ADADC-5153-440C-9AD7-FFBE30212BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A340C91-DAD7-42FC-957A-4DBC51666DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7785" yWindow="675" windowWidth="16470" windowHeight="12750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t xml:space="preserve">                         COMPONENT
 ENTITY</t>
@@ -48,6 +48,12 @@
   </si>
   <si>
     <t>Steuert die Debug Kamera ( Bewegung und Zoom)</t>
+  </si>
+  <si>
+    <t>Bounds</t>
+  </si>
+  <si>
+    <t>Player</t>
   </si>
 </sst>
 </file>
@@ -86,7 +92,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -103,6 +109,12 @@
         <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -187,7 +199,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="2" applyFont="1" applyBorder="1"/>
@@ -215,6 +227,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Neutral" xfId="2" builtinId="28"/>
@@ -522,19 +535,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" customWidth="1"/>
-    <col min="5" max="6" width="11.140625" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.33203125" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" customWidth="1"/>
+    <col min="5" max="6" width="11.109375" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" customWidth="1"/>
+    <col min="10" max="10" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -549,7 +562,7 @@
       <c r="H2" s="10"/>
       <c r="I2" s="11"/>
     </row>
-    <row r="3" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -564,7 +577,7 @@
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -579,7 +592,7 @@
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
@@ -589,7 +602,7 @@
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
@@ -599,7 +612,7 @@
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -609,7 +622,7 @@
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -619,7 +632,7 @@
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -629,7 +642,7 @@
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -639,7 +652,7 @@
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -649,7 +662,7 @@
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -659,7 +672,7 @@
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -669,7 +682,7 @@
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -679,7 +692,7 @@
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -689,7 +702,7 @@
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -699,7 +712,7 @@
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
@@ -709,12 +722,14 @@
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
     </row>
-    <row r="19" spans="1:11" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:11" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:11" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="4"/>
+      <c r="B20" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -725,7 +740,7 @@
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
     </row>
-    <row r="21" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>4</v>
       </c>
@@ -740,7 +755,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
     </row>
-    <row r="22" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>6</v>
       </c>
@@ -755,7 +770,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
     </row>
-    <row r="23" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -768,7 +783,7 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
-    <row r="24" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -781,7 +796,7 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
     </row>
-    <row r="25" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5"/>
       <c r="B25" s="1"/>
       <c r="C25" s="7"/>
@@ -794,7 +809,7 @@
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
     </row>
-    <row r="26" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -807,7 +822,7 @@
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
     </row>
-    <row r="27" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -820,7 +835,7 @@
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
     </row>
-    <row r="28" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -833,7 +848,7 @@
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
     </row>
-    <row r="29" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -846,7 +861,7 @@
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
     </row>
-    <row r="30" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -859,7 +874,7 @@
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
     </row>
-    <row r="31" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -872,7 +887,7 @@
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
     </row>
-    <row r="32" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -885,13 +900,15 @@
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
     </row>
-    <row r="33" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:11" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="1:11" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="4"/>
+      <c r="B39" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -902,9 +919,11 @@
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
     </row>
-    <row r="40" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="5"/>
-      <c r="B40" s="1"/>
+    <row r="40" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="13"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
@@ -915,7 +934,7 @@
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
     </row>
-    <row r="41" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="5"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -928,7 +947,7 @@
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
     </row>
-    <row r="42" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -941,7 +960,7 @@
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
     </row>
-    <row r="43" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:11" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="B17:I17"/>
@@ -966,7 +985,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -975,7 +994,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
